--- a/docx/รายการประเมินความพึงพอใจ.xlsx
+++ b/docx/รายการประเมินความพึงพอใจ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\devaree_project\docx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B25A1DCF-D8F6-4DE1-9633-456517101D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5A6AA1-DD36-4274-BE82-12CC8C94B5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4DF00393-438B-4B87-92DD-8BA430E2B612}"/>
   </bookViews>
@@ -42,9 +42,6 @@
     <t>𝑋̅</t>
   </si>
   <si>
-    <t>S.D</t>
-  </si>
-  <si>
     <t>1. ด้านการออกแบบของระบบ</t>
   </si>
   <si>
@@ -109,6 +106,9 @@
   </si>
   <si>
     <t>4.4 สามารถนำไปประยุกต์ใช้กับร้านอื่น ๆ</t>
+  </si>
+  <si>
+    <t>S.D.</t>
   </si>
 </sst>
 </file>
@@ -218,6 +218,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -225,9 +228,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -559,181 +559,181 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="4" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A3" s="7" t="s">
-        <v>4</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A4" s="7" t="s">
-        <v>5</v>
+      <c r="A4" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A5" s="7" t="s">
-        <v>6</v>
+      <c r="A5" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A6" s="7" t="s">
-        <v>7</v>
+      <c r="A6" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+    </row>
+    <row r="9" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A9" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-    </row>
-    <row r="9" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A9" s="7" t="s">
-        <v>10</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A10" s="7" t="s">
-        <v>13</v>
+      <c r="A10" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A11" s="7" t="s">
-        <v>12</v>
+      <c r="A11" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A12" s="7" t="s">
-        <v>11</v>
+      <c r="A12" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+    </row>
+    <row r="15" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A15" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
-    </row>
-    <row r="15" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A15" s="7" t="s">
-        <v>15</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A16" s="7" t="s">
-        <v>16</v>
+      <c r="A16" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A17" s="7" t="s">
-        <v>17</v>
+      <c r="A17" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
+      <c r="A19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A20" s="7" t="s">
-        <v>21</v>
+      <c r="A20" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A21" s="7" t="s">
-        <v>22</v>
+      <c r="A21" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A22" s="7" t="s">
-        <v>23</v>
+      <c r="A22" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A23" s="7" t="s">
-        <v>24</v>
+      <c r="A23" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
     </row>
     <row r="24" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A24" s="7" t="s">
-        <v>19</v>
+      <c r="A24" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
     </row>
     <row r="25" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A26" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
